--- a/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,18</t>
+          <t>0,98; 6,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,26</t>
+          <t>0,6; 3,12</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,94</t>
+          <t>0,47; 3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,56</t>
+          <t>0,41; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,96</t>
+          <t>0,73; 3,2</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,64</t>
+          <t>0,54; 4,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,95</t>
+          <t>0,44; 3,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,23</t>
+          <t>0,81; 3,22</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,7</t>
+          <t>0,27; 2,53</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,85</t>
+          <t>1,09; 2,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,05</t>
+          <t>0,59; 2,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,19</t>
+          <t>0,94; 2,16</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1137; 7438</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2479</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1526; 7874</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3184</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6756</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>879; 7371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1018; 9220</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3186; 14011</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2691</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6365</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1013; 7864</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>791; 6739</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2986; 11843</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 7688</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5919</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>915; 8566</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20477</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7131; 19227</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4420; 15600</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13156; 30099</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,39</t>
+          <t>1,01; 6,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,12</t>
+          <t>0,64; 3,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,94</t>
+          <t>0,54; 3,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,67</t>
+          <t>0,43; 3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,2</t>
+          <t>0,69; 3,16</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,18</t>
+          <t>0,66; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,76</t>
+          <t>0,45; 4,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,22</t>
+          <t>0,86; 3,3</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,53</t>
+          <t>0,35; 2,46</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,95</t>
+          <t>1,05; 2,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,1</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,16</t>
+          <t>0,98; 2,21</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1137; 7438</t>
+          <t>1173; 6978</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2479</t>
+          <t>0; 2756</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1526; 7874</t>
+          <t>1626; 8667</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>879; 7371</t>
+          <t>1006; 7307</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1018; 9220</t>
+          <t>1072; 9630</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3186; 14011</t>
+          <t>3031; 13849</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1013; 7864</t>
+          <t>1248; 8609</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>791; 6739</t>
+          <t>808; 7638</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2986; 11843</t>
+          <t>3162; 12110</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7688</t>
+          <t>0; 7355</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5919</t>
+          <t>0; 5350</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>915; 8566</t>
+          <t>1195; 8304</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7131; 19227</t>
+          <t>6830; 19183</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4420; 15600</t>
+          <t>4295; 14694</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13156; 30099</t>
+          <t>13705; 30855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,0</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>1,13; 6,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,43</t>
+          <t>0,75; 3,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,91</t>
+          <t>0,29; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,83</t>
+          <t>0,59; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,16</t>
+          <t>0,66; 3,03</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,58</t>
+          <t>0,38; 3,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,26</t>
+          <t>0,9; 5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,3</t>
+          <t>0,88; 3,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,46</t>
+          <t>0,29; 2,87</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,94</t>
+          <t>0,54; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>1,2; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,21</t>
+          <t>1,04; 2,27</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4081</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1173; 6978</t>
+          <t>0; 3161</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2756</t>
+          <t>1354; 7726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1626; 8667</t>
+          <t>1809; 8429</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6584</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1006; 7307</t>
+          <t>687; 9002</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1072; 9630</t>
+          <t>1061; 7417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3031; 13849</t>
+          <t>2739; 12542</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>5780</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1248; 8609</t>
+          <t>621; 6067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>808; 7638</t>
+          <t>1389; 8243</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3162; 12110</t>
+          <t>2778; 10800</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3623</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7355</t>
+          <t>0; 5520</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5350</t>
+          <t>0; 7949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1195; 8304</t>
+          <t>941; 9378</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>20068</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6830; 19183</t>
+          <t>3669; 14550</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4295; 14694</t>
+          <t>7390; 18687</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13705; 30855</t>
+          <t>13498; 29527</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,6</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 6,42</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 3,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 3,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 4,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,66; 3,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 3,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,9; 5,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 3,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,33</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,94</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 2,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 2,13</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 3,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,04; 2,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.004329789335739485</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.02953813089628108</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.01685636559450631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4081</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01125277551024786</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.007470867100430548</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3161</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1354; 7726</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1809; 8429</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.0259546338704181</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.06421663019833942</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.03481184652785758</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01495530829121688</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01709334018131283</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01588852338380175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3092</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6584</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.002940584764738349</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.005867733945224178</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.006609892620539196</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>687; 9002</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1061; 7417</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2739; 12542</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03855008484109552</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.04100579767781117</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03026667401240165</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.0133825795101031</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.02335783993522803</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01825813054069697</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2166</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3614</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5780</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.003836706990501389</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.008979512186482245</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.00877633460537316</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>621; 6067</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1389; 8243</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2778; 10800</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.03748743462167254</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.05327169490513586</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03411433364527369</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.009405621802036549</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.0128103894802039</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01108229468139249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3623</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.002877722891897527</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>0; 5520</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 7949</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>941; 9378</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.03326707781791379</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.04937426828323686</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02868731249378111</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01133986487354178</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01997401602472994</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01543716156612405</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>7746</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12322</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20068</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.005370905468980438</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.01197890024747028</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01038343752593734</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>3669; 14550</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>7390; 18687</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13498; 29527</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02130044680734736</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.03029072834385894</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02271324652790862</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>527</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3554</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3161</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7726</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>8429</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3492</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3092</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6584</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>687</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1061</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9002</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>7417</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12542</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2166</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3614</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5780</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>621</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1389</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>6067</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8243</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1561</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>2062</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>5520</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>7949</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9378</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>7746</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>12322</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>20068</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>3669</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>7390</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>13498</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>14550</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>18687</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>29527</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>